--- a/12625728.xlsx
+++ b/12625728.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4C486E2-B34F-44B7-9D83-5714663A7A99}"/>
+  <xr:revisionPtr revIDLastSave="221" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C73973D1-BBFD-4FEE-85AA-1633C648AA10}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1720,25 +1720,43 @@
       <c r="N20" s="16"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="A21" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B21" s="13">
+        <v>390</v>
+      </c>
+      <c r="C21" s="13">
+        <v>60</v>
+      </c>
+      <c r="D21" s="13">
+        <v>300</v>
+      </c>
+      <c r="E21" s="13">
+        <v>90</v>
+      </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="14" t="str">
+      <c r="H21" s="13">
+        <v>300</v>
+      </c>
+      <c r="I21" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="14" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J21" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
+        <v>300</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="N21" s="16"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">

--- a/12625728.xlsx
+++ b/12625728.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C73973D1-BBFD-4FEE-85AA-1633C648AA10}"/>
+  <xr:revisionPtr revIDLastSave="231" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{516DF276-8C54-4203-90B8-106C267A553C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1760,25 +1760,43 @@
       <c r="N21" s="16"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="A22" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B22" s="13">
+        <v>360</v>
+      </c>
+      <c r="C22" s="13">
+        <v>60</v>
+      </c>
+      <c r="D22" s="13">
+        <v>240</v>
+      </c>
+      <c r="E22" s="13">
+        <v>90</v>
+      </c>
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14" t="str">
+      <c r="H22" s="13">
+        <v>330</v>
+      </c>
+      <c r="I22" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="14" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J22" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
+        <v>360</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="15" t="s">
+        <v>61</v>
+      </c>
       <c r="N22" s="16"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">

--- a/12625728.xlsx
+++ b/12625728.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="231" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{516DF276-8C54-4203-90B8-106C267A553C}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4315E8FA-4834-4DEC-BDD9-154AA9DA1EA2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1800,25 +1800,47 @@
       <c r="N22" s="16"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14" t="str">
+      <c r="A23" s="12">
+        <v>46286</v>
+      </c>
+      <c r="B23" s="13">
+        <v>360</v>
+      </c>
+      <c r="C23" s="13">
+        <v>60</v>
+      </c>
+      <c r="D23" s="13">
+        <v>180</v>
+      </c>
+      <c r="E23" s="13">
+        <v>90</v>
+      </c>
+      <c r="F23" s="13">
+        <v>300</v>
+      </c>
+      <c r="G23" s="13">
+        <v>6</v>
+      </c>
+      <c r="H23" s="13">
+        <v>240</v>
+      </c>
+      <c r="I23" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="14" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J23" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
+        <v>210</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="N23" s="16"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">

--- a/12625728.xlsx
+++ b/12625728.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4315E8FA-4834-4DEC-BDD9-154AA9DA1EA2}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97DD19D4-A21B-447F-8D3F-3A917F78C40C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1844,25 +1844,47 @@
       <c r="N23" s="16"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14" t="str">
+      <c r="A24" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B24" s="13">
+        <v>360</v>
+      </c>
+      <c r="C24" s="13">
+        <v>60</v>
+      </c>
+      <c r="D24" s="13">
+        <v>300</v>
+      </c>
+      <c r="E24" s="13">
+        <v>45</v>
+      </c>
+      <c r="F24" s="13">
+        <v>350</v>
+      </c>
+      <c r="G24" s="13">
+        <v>7</v>
+      </c>
+      <c r="H24" s="13">
+        <v>230</v>
+      </c>
+      <c r="I24" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="14" t="str">
+        <v>1345</v>
+      </c>
+      <c r="J24" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
+        <v>95</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="N24" s="16"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">

--- a/12625728.xlsx
+++ b/12625728.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97DD19D4-A21B-447F-8D3F-3A917F78C40C}"/>
+  <xr:revisionPtr revIDLastSave="269" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1813101F-6687-4B79-B789-BF49120E9C17}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t xml:space="preserve"> I was awere of answer but gave very poor performance </t>
+  </si>
+  <si>
+    <t>both the ca were fine</t>
   </si>
 </sst>
 </file>
@@ -1888,26 +1891,50 @@
       <c r="N24" s="16"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="14" t="str">
+      <c r="A25" s="12">
+        <v>46288</v>
+      </c>
+      <c r="B25" s="13">
+        <v>240</v>
+      </c>
+      <c r="C25" s="13">
+        <v>60</v>
+      </c>
+      <c r="D25" s="13">
+        <v>330</v>
+      </c>
+      <c r="E25" s="13">
+        <v>90</v>
+      </c>
+      <c r="F25" s="13">
+        <v>300</v>
+      </c>
+      <c r="G25" s="13">
+        <v>6</v>
+      </c>
+      <c r="H25" s="13">
+        <v>200</v>
+      </c>
+      <c r="I25" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="14" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J25" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="12"/>

--- a/12625728.xlsx
+++ b/12625728.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="269" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1813101F-6687-4B79-B789-BF49120E9C17}"/>
+  <xr:revisionPtr revIDLastSave="280" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78F9ABF6-E2FE-45A2-8607-A434CFF2ECA2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1937,25 +1937,47 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="14" t="str">
+      <c r="A26" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B26" s="13">
+        <v>420</v>
+      </c>
+      <c r="C26" s="13">
+        <v>60</v>
+      </c>
+      <c r="D26" s="13">
+        <v>300</v>
+      </c>
+      <c r="E26" s="13">
+        <v>90</v>
+      </c>
+      <c r="F26" s="13">
+        <v>100</v>
+      </c>
+      <c r="G26" s="13">
+        <v>2</v>
+      </c>
+      <c r="H26" s="13">
+        <v>180</v>
+      </c>
+      <c r="I26" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="14" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J26" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
+        <v>290</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="N26" s="16"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">

--- a/12625728.xlsx
+++ b/12625728.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="280" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78F9ABF6-E2FE-45A2-8607-A434CFF2ECA2}"/>
+  <xr:revisionPtr revIDLastSave="296" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67459659-F97A-47B8-8BD2-C6C1E2131A6A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1738,8 +1738,12 @@
       <c r="E21" s="13">
         <v>90</v>
       </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
+      <c r="F21" s="13">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13">
+        <v>0</v>
+      </c>
       <c r="H21" s="13">
         <v>300</v>
       </c>
@@ -1778,8 +1782,12 @@
       <c r="E22" s="13">
         <v>90</v>
       </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
+      <c r="F22" s="13">
+        <v>0</v>
+      </c>
+      <c r="G22" s="13">
+        <v>0</v>
+      </c>
       <c r="H22" s="13">
         <v>330</v>
       </c>
@@ -1981,25 +1989,47 @@
       <c r="N26" s="16"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="12"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14" t="str">
+      <c r="A27" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B27" s="13">
+        <v>300</v>
+      </c>
+      <c r="C27" s="13">
+        <v>60</v>
+      </c>
+      <c r="D27" s="13">
+        <v>240</v>
+      </c>
+      <c r="E27" s="13">
+        <v>90</v>
+      </c>
+      <c r="F27" s="13">
+        <v>250</v>
+      </c>
+      <c r="G27" s="13">
+        <v>5</v>
+      </c>
+      <c r="H27" s="13">
+        <v>200</v>
+      </c>
+      <c r="I27" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="14" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J27" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
+        <v>300</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="N27" s="16"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">

--- a/12625728.xlsx
+++ b/12625728.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="296" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67459659-F97A-47B8-8BD2-C6C1E2131A6A}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5393B74D-6212-44B7-86D2-FF610820DF04}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2033,25 +2033,47 @@
       <c r="N27" s="16"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="12"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="14" t="str">
+      <c r="A28" s="12">
+        <v>46291</v>
+      </c>
+      <c r="B28" s="13">
+        <v>300</v>
+      </c>
+      <c r="C28" s="13">
+        <v>60</v>
+      </c>
+      <c r="D28" s="13">
+        <v>300</v>
+      </c>
+      <c r="E28" s="13">
+        <v>90</v>
+      </c>
+      <c r="F28" s="13">
+        <v>150</v>
+      </c>
+      <c r="G28" s="13">
+        <v>3</v>
+      </c>
+      <c r="H28" s="13">
+        <v>180</v>
+      </c>
+      <c r="I28" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="14" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J28" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
+        <v>360</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="N28" s="16"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">

--- a/12625728.xlsx
+++ b/12625728.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="307" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5393B74D-6212-44B7-86D2-FF610820DF04}"/>
+  <xr:revisionPtr revIDLastSave="318" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBBA02E1-7CBE-4E1C-820D-9D3ACA585126}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2077,25 +2077,47 @@
       <c r="N28" s="16"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="14" t="str">
+      <c r="A29" s="12">
+        <v>46657</v>
+      </c>
+      <c r="B29" s="13">
+        <v>360</v>
+      </c>
+      <c r="C29" s="13">
+        <v>60</v>
+      </c>
+      <c r="D29" s="13">
+        <v>240</v>
+      </c>
+      <c r="E29" s="13">
+        <v>45</v>
+      </c>
+      <c r="F29" s="13">
+        <v>0</v>
+      </c>
+      <c r="G29" s="13">
+        <v>0</v>
+      </c>
+      <c r="H29" s="13">
+        <v>240</v>
+      </c>
+      <c r="I29" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="14" t="str">
+        <v>945</v>
+      </c>
+      <c r="J29" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
+        <v>495</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="N29" s="16"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">

--- a/12625728.xlsx
+++ b/12625728.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="318" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBBA02E1-7CBE-4E1C-820D-9D3ACA585126}"/>
+  <xr:revisionPtr revIDLastSave="331" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59E2CD54-C7DF-4B62-AA2C-2CA76ADC2C0F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>both the ca were fine</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -2121,25 +2124,47 @@
       <c r="N29" s="16"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="14" t="str">
+      <c r="A30" s="12">
+        <v>46293</v>
+      </c>
+      <c r="B30" s="13">
+        <v>360</v>
+      </c>
+      <c r="C30" s="13">
+        <v>0</v>
+      </c>
+      <c r="D30" s="13">
+        <v>0</v>
+      </c>
+      <c r="E30" s="13">
+        <v>0</v>
+      </c>
+      <c r="F30" s="13">
+        <v>0</v>
+      </c>
+      <c r="G30" s="13">
+        <v>0</v>
+      </c>
+      <c r="H30" s="13">
+        <v>600</v>
+      </c>
+      <c r="I30" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="14" t="str">
+        <v>960</v>
+      </c>
+      <c r="J30" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
+        <v>480</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="N30" s="16"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
